--- a/survey_templates/016_supplier_contract_performance_evaluation_form--survey_templates.xlsx
+++ b/survey_templates/016_supplier_contract_performance_evaluation_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>supplier_contract_review_comments</t>
+          <t>supplier_contract_review_comments_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Comments on the supplier contract</t>
+          <t>Supplier Contract Review Comments 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Contract value</t>
+          <t>Contract value (2)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>contract_start_date</t>
+          <t>contract_start_date_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Contract start date</t>
+          <t>Contract Start Date 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>contract_end_date</t>
+          <t>contract_end_date_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Contract end date</t>
+          <t>Contract End Date 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1217,8 +1217,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Not sure'}</t>
+          <t>Not sure</t>
         </is>
       </c>
     </row>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'service_contract'}</t>
+          <t>service_contract</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Service contract'}</t>
+          <t>Service contract</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'goods_contract'}</t>
+          <t>goods_contract</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Goods contract'}</t>
+          <t>Goods contract</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1586,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1603,12 +1603,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'In progress'}</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -1620,12 +1620,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'canceled'}</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Canceled'}</t>
+          <t>Canceled</t>
         </is>
       </c>
     </row>
